--- a/clients/encore/testcases/item-search/item-search-product-search-filters.xlsx
+++ b/clients/encore/testcases/item-search/item-search-product-search-filters.xlsx
@@ -366,7 +366,7 @@
     <t>Pass:10 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-09-03</t>
+    <t>Last Updated: 2026-09-04</t>
   </si>
 </sst>
 </file>
